--- a/artfynd/A 21245-2025 artfynd.xlsx
+++ b/artfynd/A 21245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127403647</v>
       </c>
       <c r="B2" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127403661</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21245-2025 artfynd.xlsx
+++ b/artfynd/A 21245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127403647</v>
       </c>
       <c r="B2" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127403661</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21245-2025 artfynd.xlsx
+++ b/artfynd/A 21245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127403647</v>
       </c>
       <c r="B2" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127403661</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21245-2025 artfynd.xlsx
+++ b/artfynd/A 21245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127403647</v>
       </c>
       <c r="B2" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127403661</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21245-2025 artfynd.xlsx
+++ b/artfynd/A 21245-2025 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127403647</v>
+        <v>127403661</v>
       </c>
       <c r="B2" t="n">
-        <v>56864</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591664</v>
+        <v>591668</v>
       </c>
       <c r="R2" t="n">
-        <v>6984660</v>
+        <v>6984674</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,45 +772,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127403661</v>
+        <v>127403647</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Svartabborrtjärnen, Svartabborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591668</v>
+        <v>591664</v>
       </c>
       <c r="R3" t="n">
-        <v>6984674</v>
+        <v>6984660</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 21245-2025 artfynd.xlsx
+++ b/artfynd/A 21245-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127403661</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127403647</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>